--- a/Figure_Plot/figure_plot_S1/settings_sequence.xlsx
+++ b/Figure_Plot/figure_plot_S1/settings_sequence.xlsx
@@ -207,8 +207,8 @@
         <a:cs typeface=""/>
         <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
         <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="SimSun" script="Hans"/>
+        <a:font typeface="PMingLiU" script="Hant"/>
         <a:font typeface="Times New Roman" script="Arab"/>
         <a:font typeface="Times New Roman" script="Hebr"/>
         <a:font typeface="Tahoma" script="Thai"/>
@@ -242,8 +242,8 @@
         <a:cs typeface=""/>
         <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
         <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="SimSun" script="Hans"/>
+        <a:font typeface="PMingLiU" script="Hant"/>
         <a:font typeface="Arial" script="Arab"/>
         <a:font typeface="Arial" script="Hebr"/>
         <a:font typeface="Tahoma" script="Thai"/>
